--- a/config/PCS_450.xlsx
+++ b/config/PCS_450.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24111" windowHeight="11268" activeTab="3"/>
+    <workbookView windowWidth="24111" windowHeight="11268" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="遥信" sheetId="4" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="28">
   <si>
     <t>序号</t>
   </si>
@@ -106,6 +106,9 @@
 2 恒压充电
 3 恒功率充电
 4 直流恒压模式</t>
+  </si>
+  <si>
+    <t>HoldingRegisters</t>
   </si>
   <si>
     <t>故障复位</t>
@@ -1557,7 +1560,7 @@
         <v>301</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>13</v>
@@ -1627,7 +1630,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>11</v>
@@ -1636,7 +1639,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>13</v>
@@ -1653,7 +1656,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>11</v>
@@ -1662,7 +1665,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>13</v>

--- a/config/PCS_450.xlsx
+++ b/config/PCS_450.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24111" windowHeight="11268" activeTab="2"/>
+    <workbookView windowHeight="15438"/>
   </bookViews>
   <sheets>
     <sheet name="遥信" sheetId="4" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
   <si>
     <t>序号</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>寄存器类型</t>
+  </si>
+  <si>
+    <t>数量</t>
   </si>
   <si>
     <t>字节序/字序</t>
@@ -1279,7 +1282,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="9.11111111111111" style="2"/>
@@ -1287,11 +1290,11 @@
     <col min="3" max="5" width="9.11111111111111" style="2"/>
     <col min="6" max="6" width="10.957264957265" style="2" customWidth="1"/>
     <col min="7" max="7" width="17.1709401709402" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.7435897435897" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.11111111111111" style="2"/>
+    <col min="8" max="9" width="11.7435897435897" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.11111111111111" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1322,30 +1325,36 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:10">
+    <row r="2" s="2" customFormat="1" spans="1:11">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2">
         <v>81</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="2">
-        <v>1</v>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="J2" s="2">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1358,7 +1367,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="9.11111111111111" style="2"/>
@@ -1366,11 +1375,11 @@
     <col min="3" max="5" width="9.11111111111111" style="2"/>
     <col min="6" max="6" width="10.957264957265" style="2" customWidth="1"/>
     <col min="7" max="7" width="17.3931623931624" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.7435897435897" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.11111111111111" style="2"/>
+    <col min="8" max="9" width="11.7435897435897" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.11111111111111" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1401,91 +1410,103 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="2">
         <v>201</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="2">
+        <v>18</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="2">
         <v>0.1</v>
       </c>
-      <c r="J2" s="2">
+      <c r="K2" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" s="2">
         <v>202</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="2">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="2">
         <v>0.1</v>
       </c>
-      <c r="J3" s="2">
+      <c r="K3" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" s="2">
         <v>203</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="2">
+        <v>18</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="2">
         <v>0.1</v>
       </c>
-      <c r="J4" s="2">
+      <c r="K4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1498,7 +1519,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="9.11111111111111" style="2"/>
@@ -1507,11 +1528,11 @@
     <col min="5" max="5" width="20.8974358974359" style="2" customWidth="1"/>
     <col min="6" max="6" width="10.957264957265" style="2" customWidth="1"/>
     <col min="7" max="7" width="17.3931623931624" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.7435897435897" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.11111111111111" style="2"/>
+    <col min="8" max="9" width="11.7435897435897" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.11111111111111" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1542,33 +1563,39 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="90" spans="1:10">
+    <row r="2" s="2" customFormat="1" ht="90" spans="1:11">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="2">
         <v>301</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="2">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="J2" s="2">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1581,7 +1608,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="9.11111111111111" style="2"/>
@@ -1589,11 +1616,11 @@
     <col min="3" max="5" width="9.11111111111111" style="2"/>
     <col min="6" max="6" width="10.957264957265" style="2" customWidth="1"/>
     <col min="7" max="7" width="17.3931623931624" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.7435897435897" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.11111111111111" style="2"/>
+    <col min="8" max="9" width="11.7435897435897" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.11111111111111" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1624,56 +1651,65 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:10">
+    <row r="2" s="2" customFormat="1" spans="1:11">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="2">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="J2" s="2">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:10">
+    <row r="3" s="2" customFormat="1" spans="1:11">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="2">
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="J3" s="2">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2">
         <v>0</v>
       </c>
     </row>

--- a/config/PCS_450.xlsx
+++ b/config/PCS_450.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15438"/>
+    <workbookView windowWidth="20946" windowHeight="11268"/>
   </bookViews>
   <sheets>
     <sheet name="遥信" sheetId="4" r:id="rId1"/>

--- a/config/PCS_450.xlsx
+++ b/config/PCS_450.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="20946" windowHeight="11268"/>
+    <workbookView windowWidth="31939" windowHeight="15438" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="遥信" sheetId="4" r:id="rId1"/>
-    <sheet name="遥测" sheetId="1" r:id="rId2"/>
+    <sheet name="遥测" sheetId="1" r:id="rId1"/>
+    <sheet name="遥信" sheetId="4" r:id="rId2"/>
     <sheet name="遥调" sheetId="5" r:id="rId3"/>
     <sheet name="遥控" sheetId="6" r:id="rId4"/>
   </sheets>
@@ -65,6 +65,33 @@
     <t>偏移量</t>
   </si>
   <si>
+    <t>PCS端口A相电压</t>
+  </si>
+  <si>
+    <t>U16</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>InputRegisters</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>PCS端口B相电压</t>
+  </si>
+  <si>
+    <t>PCS端口C相电压</t>
+  </si>
+  <si>
+    <t>U32</t>
+  </si>
+  <si>
+    <t>ABCD</t>
+  </si>
+  <si>
     <t>停机状态</t>
   </si>
   <si>
@@ -72,33 +99,6 @@
   </si>
   <si>
     <t>DiscreteInputs</t>
-  </si>
-  <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>PCS端口A相电压</t>
-  </si>
-  <si>
-    <t>U16</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>InputRegisters</t>
-  </si>
-  <si>
-    <t>PCS端口B相电压</t>
-  </si>
-  <si>
-    <t>PCS端口C相电压</t>
-  </si>
-  <si>
-    <t>U32</t>
-  </si>
-  <si>
-    <t>ABCD</t>
   </si>
   <si>
     <t>运行模式选择</t>
@@ -1282,6 +1282,158 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="1" width="9.11111111111111" style="2"/>
+    <col min="2" max="2" width="19.5213675213675" style="2" customWidth="1"/>
+    <col min="3" max="5" width="9.11111111111111" style="2"/>
+    <col min="6" max="6" width="10.957264957265" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.3931623931624" style="2" customWidth="1"/>
+    <col min="8" max="9" width="11.7435897435897" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.11111111111111" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2">
+        <v>201</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2">
+        <v>202</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2">
+        <v>203</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="1"/>
   <cols>
@@ -1331,182 +1483,30 @@
     </row>
     <row r="2" s="2" customFormat="1" spans="1:11">
       <c r="A2" s="2">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F2" s="2">
         <v>81</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H2" s="2">
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2" s="2">
         <v>1</v>
       </c>
       <c r="K2" s="2">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="3"/>
-  <cols>
-    <col min="1" max="1" width="9.11111111111111" style="2"/>
-    <col min="2" max="2" width="19.5213675213675" style="2" customWidth="1"/>
-    <col min="3" max="5" width="9.11111111111111" style="2"/>
-    <col min="6" max="6" width="10.957264957265" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.3931623931624" style="2" customWidth="1"/>
-    <col min="8" max="9" width="11.7435897435897" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.11111111111111" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="2">
-        <v>201</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="2">
-        <v>202</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="K3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="2">
-        <v>203</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="2">
-        <v>2</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="K4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1569,13 +1569,13 @@
     </row>
     <row r="2" s="2" customFormat="1" ht="90" spans="1:11">
       <c r="A2" s="2">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>24</v>
@@ -1590,7 +1590,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2" s="2">
         <v>1</v>
@@ -1657,13 +1657,13 @@
     </row>
     <row r="2" s="2" customFormat="1" spans="1:11">
       <c r="A2" s="2">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -1675,7 +1675,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2" s="2">
         <v>1</v>
@@ -1686,13 +1686,13 @@
     </row>
     <row r="3" s="2" customFormat="1" spans="1:11">
       <c r="A3" s="2">
-        <v>2</v>
+        <v>3001</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F3" s="2">
         <v>2</v>
@@ -1704,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3" s="2">
         <v>1</v>
